--- a/src/data/opportunities.xlsx
+++ b/src/data/opportunities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\nomad\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA14ADA-87CB-4D6B-A037-DBC2E49791CB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482620D2-DD63-44D4-940E-2AE4BA2FC726}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E67CE06A-7ED6-442D-9A1D-2B8451E04010}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="109">
   <si>
     <t>SS</t>
   </si>
@@ -69,12 +69,6 @@
     <t>Çexiya</t>
   </si>
   <si>
-    <t>30.06.2026</t>
-  </si>
-  <si>
-    <t>Tunis</t>
-  </si>
-  <si>
     <t>05.07.2026</t>
   </si>
   <si>
@@ -90,75 +84,16 @@
     <t>İsveç</t>
   </si>
   <si>
-    <t>Beyond Take Off: From Local Youth Work to Cross Border Connections</t>
-  </si>
-  <si>
-    <t>28.06.2026</t>
-  </si>
-  <si>
     <t>Gürcüstan</t>
   </si>
   <si>
-    <t>http://trainings.salto-youth.net/14941</t>
-  </si>
-  <si>
-    <t>07.08.2026</t>
-  </si>
-  <si>
-    <t>Europe as a Resource for Local Youth Work</t>
-  </si>
-  <si>
-    <t>Estoniya</t>
-  </si>
-  <si>
-    <t>http://trainings.salto-youth.net/14994</t>
-  </si>
-  <si>
     <t>17.07.2026</t>
   </si>
   <si>
-    <t>Strengthening Local Youth Councils in the AI age</t>
-  </si>
-  <si>
-    <t>http://trainings.salto-youth.net/14970</t>
-  </si>
-  <si>
     <t>03.07.2026</t>
   </si>
   <si>
-    <t>Connect &amp; Create: KA220 Partnership Lab</t>
-  </si>
-  <si>
-    <t>http://trainings.salto-youth.net/14971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exchange Forum on the European Youth Work Agenda: Boosting national processes for youth work development
-</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>http://trainings.salto-youth.net/14958</t>
-  </si>
-  <si>
-    <t>03.09.2026</t>
-  </si>
-  <si>
-    <t>Supporting ESC Volunteers through Mentoring Training Course</t>
-  </si>
-  <si>
-    <t>http://trainings.salto-youth.net/14895</t>
-  </si>
-  <si>
     <t>15.07.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Youth@Work Conference: Value and Recognition of Youth Work for Employability and Entrepreneurship
-</t>
-  </si>
-  <si>
-    <t>http://trainings.salto-youth.net/14923</t>
   </si>
   <si>
     <t>16.07.2026</t>
@@ -480,7 +415,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,12 +425,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDFDFD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,7 +508,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -609,12 +538,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -932,13 +855,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B4CD96-AC7D-492E-AE06-0EAE7F0BDEC4}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.44140625" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -967,111 +891,111 @@
     </row>
     <row r="2" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>43</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>44</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>20</v>
+        <v>51</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>17</v>
+      <c r="E4" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
-        <v>45</v>
-      </c>
-      <c r="B5" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>20</v>
+      <c r="C5" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>8</v>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>32</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
-        <v>46</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>34</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>35</v>
@@ -1082,19 +1006,19 @@
     </row>
     <row r="7" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>47</v>
-      </c>
-      <c r="B7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>20</v>
+      <c r="C7" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>13</v>
+      <c r="E7" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>38</v>
@@ -1103,67 +1027,67 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>12</v>
+      <c r="C8" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>14</v>
+      <c r="C10" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>48</v>
@@ -1172,572 +1096,404 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>7</v>
+      <c r="C11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>7</v>
+        <v>55</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>15</v>
+        <v>62</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
         <v>64</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4">
-        <v>57</v>
-      </c>
       <c r="B17" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>10</v>
+        <v>75</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>10</v>
+        <v>79</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>7</v>
+        <v>92</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>101</v>
+        <v>106</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>103</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
-        <v>67</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="6" t="s">
         <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="4">
-        <v>68</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="4">
-        <v>69</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="4">
-        <v>70</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="4">
-        <v>71</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="4">
-        <v>72</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="4">
-        <v>73</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{3B94C599-A78F-4462-A73C-CF284B143E4B}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{633B9331-88B3-4A37-8AF4-CC7A89000B8F}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{2502FCF8-7B3C-4546-A76A-DA23F26BFFF1}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{6A2FCB26-527C-479E-8926-E68F8D335693}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{E9F0B2D3-778B-4E7C-9246-3788B0E74DB7}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{DC59F2FB-2ADD-486E-9D4E-3EE3A75CA4CA}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{8D87CB54-0478-468B-8160-7F18BFA70368}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{6881BB01-025D-4D92-B0E9-68DAD5EEA001}"/>
-    <hyperlink ref="F10" r:id="rId9" xr:uid="{37F8BB63-9243-41C4-A9A4-0989742000DB}"/>
-    <hyperlink ref="F11" r:id="rId10" xr:uid="{D6E61FDC-7D67-4285-9E49-6992F156B05F}"/>
-    <hyperlink ref="F12" r:id="rId11" display="http://trainings.salto-youth.net/15015" xr:uid="{FBDBB3F7-3DC9-450E-BAB7-9F0E146AB095}"/>
-    <hyperlink ref="F13" r:id="rId12" xr:uid="{5A8D0C2B-C65C-47FE-91A1-9B044D8338C3}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{A33BC50F-A867-4839-BAB7-771C149ED289}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{C10932C3-EB86-4707-B22A-9DA5B87421AE}"/>
-    <hyperlink ref="F16" r:id="rId15" xr:uid="{BB74DBFF-F776-41A3-8CFF-4851AFE06B50}"/>
-    <hyperlink ref="F17" r:id="rId16" xr:uid="{1FFC2B95-5C9C-4C02-BE65-FF024418D5FB}"/>
-    <hyperlink ref="F18" r:id="rId17" xr:uid="{9E4D1AB9-F355-45B6-8C69-5A81618E05C6}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{D3D03596-F300-4558-BC22-9E020DA39366}"/>
-    <hyperlink ref="F20" r:id="rId19" display="http://trainings.salto-youth.net/15026" xr:uid="{AC91A2FE-B548-4F14-8232-3A338DB282E9}"/>
-    <hyperlink ref="F21" r:id="rId20" xr:uid="{C78B5798-053C-42DB-821D-56A3CD4B67D8}"/>
-    <hyperlink ref="F22" r:id="rId21" xr:uid="{2405E033-17BC-48E8-86A6-76D6740E295B}"/>
-    <hyperlink ref="F23" r:id="rId22" xr:uid="{C8A90438-9B97-42B5-89FC-B524E4CDC4A0}"/>
-    <hyperlink ref="F24" r:id="rId23" xr:uid="{DEADBCDA-39DD-448F-8999-9D832A33B602}"/>
-    <hyperlink ref="F25" r:id="rId24" xr:uid="{66EE0236-D3BC-4DFC-8353-BB713D0B63A5}"/>
-    <hyperlink ref="F26" r:id="rId25" xr:uid="{6A60A5D1-421A-4BE3-85BC-5E39BE2FF713}"/>
-    <hyperlink ref="F27" r:id="rId26" xr:uid="{37518343-B5D7-4755-822D-E26B58CEE090}"/>
-    <hyperlink ref="F28" r:id="rId27" xr:uid="{2A4795C2-862E-403A-A0A3-D9607ACB4381}"/>
-    <hyperlink ref="F29" r:id="rId28" xr:uid="{A8EF5969-468A-4654-9FAD-684C85C14677}"/>
-    <hyperlink ref="F30" r:id="rId29" xr:uid="{8DDEE50C-1DA8-4AF7-B6DF-7B1E0302FC72}"/>
-    <hyperlink ref="F31" r:id="rId30" xr:uid="{64C5788D-B228-4570-8B26-FAACC195A0A9}"/>
-    <hyperlink ref="F32" r:id="rId31" xr:uid="{D5385C39-02D2-410F-9F43-F71178BBD403}"/>
-    <hyperlink ref="F33" r:id="rId32" xr:uid="{C4464764-9BA0-44F9-B0D7-57AAB8881480}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{6881BB01-025D-4D92-B0E9-68DAD5EEA001}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{37F8BB63-9243-41C4-A9A4-0989742000DB}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{D6E61FDC-7D67-4285-9E49-6992F156B05F}"/>
+    <hyperlink ref="F5" r:id="rId4" display="http://trainings.salto-youth.net/15015" xr:uid="{FBDBB3F7-3DC9-450E-BAB7-9F0E146AB095}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{5A8D0C2B-C65C-47FE-91A1-9B044D8338C3}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{A33BC50F-A867-4839-BAB7-771C149ED289}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{C10932C3-EB86-4707-B22A-9DA5B87421AE}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{BB74DBFF-F776-41A3-8CFF-4851AFE06B50}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{1FFC2B95-5C9C-4C02-BE65-FF024418D5FB}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{9E4D1AB9-F355-45B6-8C69-5A81618E05C6}"/>
+    <hyperlink ref="F12" r:id="rId11" xr:uid="{D3D03596-F300-4558-BC22-9E020DA39366}"/>
+    <hyperlink ref="F13" r:id="rId12" display="http://trainings.salto-youth.net/15026" xr:uid="{AC91A2FE-B548-4F14-8232-3A338DB282E9}"/>
+    <hyperlink ref="F14" r:id="rId13" xr:uid="{C78B5798-053C-42DB-821D-56A3CD4B67D8}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{2405E033-17BC-48E8-86A6-76D6740E295B}"/>
+    <hyperlink ref="F16" r:id="rId15" xr:uid="{C8A90438-9B97-42B5-89FC-B524E4CDC4A0}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{DEADBCDA-39DD-448F-8999-9D832A33B602}"/>
+    <hyperlink ref="F18" r:id="rId17" xr:uid="{66EE0236-D3BC-4DFC-8353-BB713D0B63A5}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{6A60A5D1-421A-4BE3-85BC-5E39BE2FF713}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{37518343-B5D7-4755-822D-E26B58CEE090}"/>
+    <hyperlink ref="F21" r:id="rId20" xr:uid="{2A4795C2-862E-403A-A0A3-D9607ACB4381}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{A8EF5969-468A-4654-9FAD-684C85C14677}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{8DDEE50C-1DA8-4AF7-B6DF-7B1E0302FC72}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{64C5788D-B228-4570-8B26-FAACC195A0A9}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{D5385C39-02D2-410F-9F43-F71178BBD403}"/>
+    <hyperlink ref="F26" r:id="rId25" xr:uid="{C4464764-9BA0-44F9-B0D7-57AAB8881480}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>
--- a/src/data/opportunities.xlsx
+++ b/src/data/opportunities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\nomad\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482620D2-DD63-44D4-940E-2AE4BA2FC726}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4669432-C990-4DB9-A6EE-ADA547A328D1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E67CE06A-7ED6-442D-9A1D-2B8451E04010}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="105">
   <si>
     <t>SS</t>
   </si>
@@ -90,22 +90,10 @@
     <t>17.07.2026</t>
   </si>
   <si>
-    <t>03.07.2026</t>
-  </si>
-  <si>
     <t>15.07.2026</t>
   </si>
   <si>
     <t>16.07.2026</t>
-  </si>
-  <si>
-    <t>Transforming Challenges into Shared Happiness</t>
-  </si>
-  <si>
-    <t>02.07.2026</t>
-  </si>
-  <si>
-    <t>http://trainings.salto-youth.net/14992</t>
   </si>
   <si>
     <t>Pathways to Accessible Youth Work - Online Conference</t>
@@ -855,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B4CD96-AC7D-492E-AE06-0EAE7F0BDEC4}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
@@ -891,30 +879,30 @@
     </row>
     <row r="2" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>25</v>
@@ -922,25 +910,25 @@
       <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>10</v>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>27</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>12</v>
@@ -949,122 +937,122 @@
         <v>7</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>53</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4">
-        <v>52</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="G5" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>54</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4">
-        <v>53</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="E6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4">
-        <v>56</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>44</v>
@@ -1073,9 +1061,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>46</v>
@@ -1087,53 +1075,53 @@
         <v>10</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>60</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4">
-        <v>59</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>56</v>
@@ -1142,21 +1130,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>10</v>
+        <v>59</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>60</v>
@@ -1167,42 +1155,42 @@
     </row>
     <row r="14" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>7</v>
+      <c r="D15" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>67</v>
@@ -1213,53 +1201,53 @@
     </row>
     <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>69</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>75</v>
@@ -1271,30 +1259,30 @@
         <v>7</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>82</v>
@@ -1305,7 +1293,7 @@
     </row>
     <row r="20" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>84</v>
@@ -1317,7 +1305,7 @@
         <v>7</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>86</v>
@@ -1328,88 +1316,88 @@
     </row>
     <row r="21" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>88</v>
       </c>
       <c r="C21" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>96</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>10</v>
+        <v>99</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>100</v>
@@ -1420,80 +1408,56 @@
     </row>
     <row r="25" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F25" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4">
-        <v>73</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{6881BB01-025D-4D92-B0E9-68DAD5EEA001}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{37F8BB63-9243-41C4-A9A4-0989742000DB}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{D6E61FDC-7D67-4285-9E49-6992F156B05F}"/>
-    <hyperlink ref="F5" r:id="rId4" display="http://trainings.salto-youth.net/15015" xr:uid="{FBDBB3F7-3DC9-450E-BAB7-9F0E146AB095}"/>
-    <hyperlink ref="F6" r:id="rId5" xr:uid="{5A8D0C2B-C65C-47FE-91A1-9B044D8338C3}"/>
-    <hyperlink ref="F7" r:id="rId6" xr:uid="{A33BC50F-A867-4839-BAB7-771C149ED289}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{C10932C3-EB86-4707-B22A-9DA5B87421AE}"/>
-    <hyperlink ref="F9" r:id="rId8" xr:uid="{BB74DBFF-F776-41A3-8CFF-4851AFE06B50}"/>
-    <hyperlink ref="F10" r:id="rId9" xr:uid="{1FFC2B95-5C9C-4C02-BE65-FF024418D5FB}"/>
-    <hyperlink ref="F11" r:id="rId10" xr:uid="{9E4D1AB9-F355-45B6-8C69-5A81618E05C6}"/>
-    <hyperlink ref="F12" r:id="rId11" xr:uid="{D3D03596-F300-4558-BC22-9E020DA39366}"/>
-    <hyperlink ref="F13" r:id="rId12" display="http://trainings.salto-youth.net/15026" xr:uid="{AC91A2FE-B548-4F14-8232-3A338DB282E9}"/>
-    <hyperlink ref="F14" r:id="rId13" xr:uid="{C78B5798-053C-42DB-821D-56A3CD4B67D8}"/>
-    <hyperlink ref="F15" r:id="rId14" xr:uid="{2405E033-17BC-48E8-86A6-76D6740E295B}"/>
-    <hyperlink ref="F16" r:id="rId15" xr:uid="{C8A90438-9B97-42B5-89FC-B524E4CDC4A0}"/>
-    <hyperlink ref="F17" r:id="rId16" xr:uid="{DEADBCDA-39DD-448F-8999-9D832A33B602}"/>
-    <hyperlink ref="F18" r:id="rId17" xr:uid="{66EE0236-D3BC-4DFC-8353-BB713D0B63A5}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{6A60A5D1-421A-4BE3-85BC-5E39BE2FF713}"/>
-    <hyperlink ref="F20" r:id="rId19" xr:uid="{37518343-B5D7-4755-822D-E26B58CEE090}"/>
-    <hyperlink ref="F21" r:id="rId20" xr:uid="{2A4795C2-862E-403A-A0A3-D9607ACB4381}"/>
-    <hyperlink ref="F22" r:id="rId21" xr:uid="{A8EF5969-468A-4654-9FAD-684C85C14677}"/>
-    <hyperlink ref="F23" r:id="rId22" xr:uid="{8DDEE50C-1DA8-4AF7-B6DF-7B1E0302FC72}"/>
-    <hyperlink ref="F24" r:id="rId23" xr:uid="{64C5788D-B228-4570-8B26-FAACC195A0A9}"/>
-    <hyperlink ref="F25" r:id="rId24" xr:uid="{D5385C39-02D2-410F-9F43-F71178BBD403}"/>
-    <hyperlink ref="F26" r:id="rId25" xr:uid="{C4464764-9BA0-44F9-B0D7-57AAB8881480}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{37F8BB63-9243-41C4-A9A4-0989742000DB}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{D6E61FDC-7D67-4285-9E49-6992F156B05F}"/>
+    <hyperlink ref="F4" r:id="rId3" display="http://trainings.salto-youth.net/15015" xr:uid="{FBDBB3F7-3DC9-450E-BAB7-9F0E146AB095}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{5A8D0C2B-C65C-47FE-91A1-9B044D8338C3}"/>
+    <hyperlink ref="F6" r:id="rId5" xr:uid="{A33BC50F-A867-4839-BAB7-771C149ED289}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{C10932C3-EB86-4707-B22A-9DA5B87421AE}"/>
+    <hyperlink ref="F8" r:id="rId7" xr:uid="{BB74DBFF-F776-41A3-8CFF-4851AFE06B50}"/>
+    <hyperlink ref="F9" r:id="rId8" xr:uid="{1FFC2B95-5C9C-4C02-BE65-FF024418D5FB}"/>
+    <hyperlink ref="F10" r:id="rId9" xr:uid="{9E4D1AB9-F355-45B6-8C69-5A81618E05C6}"/>
+    <hyperlink ref="F11" r:id="rId10" xr:uid="{D3D03596-F300-4558-BC22-9E020DA39366}"/>
+    <hyperlink ref="F12" r:id="rId11" display="http://trainings.salto-youth.net/15026" xr:uid="{AC91A2FE-B548-4F14-8232-3A338DB282E9}"/>
+    <hyperlink ref="F13" r:id="rId12" xr:uid="{C78B5798-053C-42DB-821D-56A3CD4B67D8}"/>
+    <hyperlink ref="F14" r:id="rId13" xr:uid="{2405E033-17BC-48E8-86A6-76D6740E295B}"/>
+    <hyperlink ref="F15" r:id="rId14" xr:uid="{C8A90438-9B97-42B5-89FC-B524E4CDC4A0}"/>
+    <hyperlink ref="F16" r:id="rId15" xr:uid="{DEADBCDA-39DD-448F-8999-9D832A33B602}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{66EE0236-D3BC-4DFC-8353-BB713D0B63A5}"/>
+    <hyperlink ref="F18" r:id="rId17" xr:uid="{6A60A5D1-421A-4BE3-85BC-5E39BE2FF713}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{37518343-B5D7-4755-822D-E26B58CEE090}"/>
+    <hyperlink ref="F20" r:id="rId19" xr:uid="{2A4795C2-862E-403A-A0A3-D9607ACB4381}"/>
+    <hyperlink ref="F21" r:id="rId20" xr:uid="{A8EF5969-468A-4654-9FAD-684C85C14677}"/>
+    <hyperlink ref="F22" r:id="rId21" xr:uid="{8DDEE50C-1DA8-4AF7-B6DF-7B1E0302FC72}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{64C5788D-B228-4570-8B26-FAACC195A0A9}"/>
+    <hyperlink ref="F24" r:id="rId23" xr:uid="{D5385C39-02D2-410F-9F43-F71178BBD403}"/>
+    <hyperlink ref="F25" r:id="rId24" xr:uid="{C4464764-9BA0-44F9-B0D7-57AAB8881480}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>